--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/mar-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/mar-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M268"/>
+  <dimension ref="A1:M266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>16625728</v>
+        <v>18272.18</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>450819.6</v>
+        <v>495.46</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>661250.87</v>
+        <v>726.73</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8179346</v>
+        <v>8989.35</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1302722.75</v>
+        <v>1431.73</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>16358692</v>
+        <v>17978.69</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>38134198.55</v>
+        <v>41910.63</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>973779.38</v>
+        <v>1070.21</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>410816.56</v>
+        <v>451.5</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1033700.64</v>
+        <v>1136.07</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7550642.82</v>
+        <v>8298.379999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>22651928.46</v>
+        <v>24895.15</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7550642.82</v>
+        <v>8298.379999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>578389.98</v>
+        <v>635.67</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1274723.24</v>
+        <v>1400.96</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8854.799999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6911163</v>
+        <v>7595.58</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4418454.53</v>
+        <v>4856.01</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>777773.29</v>
+        <v>854.8</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>267901.13</v>
+        <v>294.43</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>410816.56</v>
+        <v>451.5</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2072807.45</v>
+        <v>2278.08</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>238474.81</v>
+        <v>262.09</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>240827.44</v>
+        <v>264.68</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>14115780</v>
+        <v>15513.67</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1995659.75</v>
+        <v>2193.29</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>591435.95</v>
+        <v>650.01</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>8072517.32</v>
+        <v>8871.940000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>586252.3100000001</v>
+        <v>644.3099999999999</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8008179.97</v>
+        <v>8801.23</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>10355637.04</v>
+        <v>11381.16</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2072861</v>
+        <v>2278.14</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4705260</v>
+        <v>5171.22</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>410816.56</v>
+        <v>451.5</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1010681.28</v>
+        <v>1110.77</v>
       </c>
     </row>
     <row r="37">
@@ -2700,11 +2700,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>16016359.94</v>
+        <v>17602.46</v>
       </c>
     </row>
     <row r="38">
@@ -2761,11 +2761,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>662544.4</v>
+        <v>728.16</v>
       </c>
     </row>
     <row r="39">
@@ -2822,11 +2822,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8854.799999999999</v>
       </c>
     </row>
     <row r="40">
@@ -2883,11 +2883,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>497034.44</v>
+        <v>546.26</v>
       </c>
     </row>
     <row r="41">
@@ -2944,11 +2944,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>33863039.84</v>
+        <v>37216.5</v>
       </c>
     </row>
     <row r="42">
@@ -3005,11 +3005,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>173664784.86</v>
+        <v>190862.82</v>
       </c>
     </row>
     <row r="43">
@@ -3066,11 +3066,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>132159.02</v>
+        <v>145.25</v>
       </c>
     </row>
     <row r="44">
@@ -3127,11 +3127,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>8179346</v>
+        <v>8989.35</v>
       </c>
     </row>
     <row r="45">
@@ -3188,11 +3188,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>839214.1800000001</v>
+        <v>922.3200000000001</v>
       </c>
     </row>
     <row r="46">
@@ -3249,11 +3249,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8179346</v>
+        <v>8989.35</v>
       </c>
     </row>
     <row r="47">
@@ -3310,11 +3310,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>608479.13</v>
+        <v>668.74</v>
       </c>
     </row>
     <row r="48">
@@ -3371,11 +3371,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>8007262.48</v>
+        <v>8800.219999999999</v>
       </c>
     </row>
     <row r="49">
@@ -3432,11 +3432,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>499800</v>
+        <v>549.3</v>
       </c>
     </row>
     <row r="50">
@@ -3493,11 +3493,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>410816.56</v>
+        <v>451.5</v>
       </c>
     </row>
     <row r="51">
@@ -3554,11 +3554,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>8312864</v>
+        <v>9136.09</v>
       </c>
     </row>
     <row r="52">
@@ -3615,11 +3615,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>634084.36</v>
+        <v>696.88</v>
       </c>
     </row>
     <row r="53">
@@ -3676,11 +3676,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>410816.56</v>
+        <v>451.5</v>
       </c>
     </row>
     <row r="54">
@@ -3737,11 +3737,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>22651928.46</v>
+        <v>24895.15</v>
       </c>
     </row>
     <row r="55">
@@ -3798,11 +3798,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>14779772.63</v>
+        <v>16243.41</v>
       </c>
     </row>
     <row r="56">
@@ -3859,11 +3859,11 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>431655.84</v>
+        <v>474.4</v>
       </c>
     </row>
     <row r="57">
@@ -3920,11 +3920,11 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>7416913</v>
+        <v>8151.41</v>
       </c>
     </row>
     <row r="58">
@@ -3981,11 +3981,11 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>22366424.85</v>
+        <v>24581.37</v>
       </c>
     </row>
     <row r="59">
@@ -4042,11 +4042,11 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>557109.21</v>
+        <v>612.28</v>
       </c>
     </row>
     <row r="60">
@@ -4103,11 +4103,11 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8854.799999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4164,11 +4164,11 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>569397.15</v>
+        <v>625.78</v>
       </c>
     </row>
     <row r="62">
@@ -4225,11 +4225,11 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>597414.51</v>
+        <v>656.58</v>
       </c>
     </row>
     <row r="63">
@@ -4286,11 +4286,11 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8854.799999999999</v>
       </c>
     </row>
     <row r="64">
@@ -4347,11 +4347,11 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>8003679.39</v>
+        <v>8796.280000000001</v>
       </c>
     </row>
     <row r="65">
@@ -4408,11 +4408,11 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>7128100</v>
+        <v>7834</v>
       </c>
     </row>
     <row r="66">
@@ -4469,11 +4469,11 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>490270.48</v>
+        <v>538.8200000000001</v>
       </c>
     </row>
     <row r="67">
@@ -4530,11 +4530,11 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>8197742.21</v>
+        <v>9009.57</v>
       </c>
     </row>
     <row r="68">
@@ -4591,11 +4591,11 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>490270.48</v>
+        <v>538.8200000000001</v>
       </c>
     </row>
     <row r="69">
@@ -4652,11 +4652,11 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>8197742.21</v>
+        <v>9009.57</v>
       </c>
     </row>
     <row r="70">
@@ -4713,11 +4713,11 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>19012927.5</v>
+        <v>20895.78</v>
       </c>
     </row>
     <row r="71">
@@ -4774,11 +4774,11 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>37377243.12</v>
+        <v>41078.71</v>
       </c>
     </row>
     <row r="72">
@@ -4835,11 +4835,11 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2337688.36</v>
+        <v>2569.19</v>
       </c>
     </row>
     <row r="73">
@@ -4896,11 +4896,11 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>54331.83</v>
+        <v>59.71</v>
       </c>
     </row>
     <row r="74">
@@ -4957,11 +4957,11 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>583830.66</v>
+        <v>641.65</v>
       </c>
     </row>
     <row r="75">
@@ -5018,11 +5018,11 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>60405142.56</v>
+        <v>66387.07000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5079,11 +5079,11 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>48022076.34</v>
+        <v>52777.71</v>
       </c>
     </row>
     <row r="77">
@@ -5140,11 +5140,11 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>6098988</v>
+        <v>6702.97</v>
       </c>
     </row>
     <row r="78">
@@ -5201,11 +5201,11 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>410816.56</v>
+        <v>451.5</v>
       </c>
     </row>
     <row r="79">
@@ -5262,11 +5262,11 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8854.799999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5323,11 +5323,11 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4326721</v>
+        <v>4755.2</v>
       </c>
     </row>
     <row r="81">
@@ -5384,11 +5384,11 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>7915628.91</v>
+        <v>8699.51</v>
       </c>
     </row>
     <row r="82">
@@ -5445,11 +5445,11 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>11846668.96</v>
+        <v>13019.85</v>
       </c>
     </row>
     <row r="83">
@@ -5506,11 +5506,11 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>752648.8199999999</v>
+        <v>827.1799999999999</v>
       </c>
     </row>
     <row r="84">
@@ -5567,11 +5567,11 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>54331.83</v>
+        <v>59.71</v>
       </c>
     </row>
     <row r="85">
@@ -5628,11 +5628,11 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>7550642.82</v>
+        <v>8298.379999999999</v>
       </c>
     </row>
     <row r="86">
@@ -5689,11 +5689,11 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3346399</v>
+        <v>3677.79</v>
       </c>
     </row>
     <row r="87">
@@ -5750,11 +5750,11 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1099266.07</v>
+        <v>1208.13</v>
       </c>
     </row>
     <row r="88">
@@ -5811,11 +5811,11 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2347394</v>
+        <v>2579.86</v>
       </c>
     </row>
     <row r="89">
@@ -5872,11 +5872,11 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>8197742.21</v>
+        <v>9009.57</v>
       </c>
     </row>
     <row r="90">
@@ -5933,11 +5933,11 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>12848275.3</v>
+        <v>14120.64</v>
       </c>
     </row>
     <row r="91">
@@ -5994,11 +5994,11 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1915266.92</v>
+        <v>2104.94</v>
       </c>
     </row>
     <row r="92">
@@ -6055,11 +6055,11 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>660897.4399999999</v>
+        <v>726.35</v>
       </c>
     </row>
     <row r="93">
@@ -6116,11 +6116,11 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>418946.64</v>
+        <v>460.43</v>
       </c>
     </row>
     <row r="94">
@@ -6177,11 +6177,11 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8854.799999999999</v>
       </c>
     </row>
     <row r="95">
@@ -6238,11 +6238,11 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>598371.27</v>
+        <v>657.63</v>
       </c>
     </row>
     <row r="96">
@@ -6299,11 +6299,11 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1283468.55</v>
+        <v>1410.57</v>
       </c>
     </row>
     <row r="97">
@@ -6360,11 +6360,11 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2466562.98</v>
+        <v>2710.83</v>
       </c>
     </row>
     <row r="98">
@@ -6421,11 +6421,11 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8854.799999999999</v>
       </c>
     </row>
     <row r="99">
@@ -6482,11 +6482,11 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>5977875.75</v>
+        <v>6569.87</v>
       </c>
     </row>
     <row r="100">
@@ -6543,11 +6543,11 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>410816.56</v>
+        <v>451.5</v>
       </c>
     </row>
     <row r="101">
@@ -6604,11 +6604,11 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>767332.23</v>
+        <v>843.3200000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6665,11 +6665,11 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>7626032.89</v>
+        <v>8381.24</v>
       </c>
     </row>
     <row r="103">
@@ -6726,11 +6726,11 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>132159.02</v>
+        <v>145.25</v>
       </c>
     </row>
     <row r="104">
@@ -6787,11 +6787,11 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>8197742.21</v>
+        <v>9009.57</v>
       </c>
     </row>
     <row r="105">
@@ -6848,11 +6848,11 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>7307552</v>
+        <v>8031.22</v>
       </c>
     </row>
     <row r="106">
@@ -6909,11 +6909,11 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>6999669.25</v>
+        <v>7692.85</v>
       </c>
     </row>
     <row r="107">
@@ -6970,11 +6970,11 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>490270.48</v>
+        <v>538.8200000000001</v>
       </c>
     </row>
     <row r="108">
@@ -7031,11 +7031,11 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>556682</v>
+        <v>611.8099999999999</v>
       </c>
     </row>
     <row r="109">
@@ -7092,11 +7092,11 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2580269.86</v>
+        <v>2835.79</v>
       </c>
     </row>
     <row r="110">
@@ -7153,11 +7153,11 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>834132.88</v>
+        <v>916.74</v>
       </c>
     </row>
     <row r="111">
@@ -7214,11 +7214,11 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>7550642.82</v>
+        <v>8298.379999999999</v>
       </c>
     </row>
     <row r="112">
@@ -7275,11 +7275,11 @@
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>7626839.71</v>
+        <v>8382.129999999999</v>
       </c>
     </row>
     <row r="113">
@@ -7336,11 +7336,11 @@
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2326778.44</v>
+        <v>2557.2</v>
       </c>
     </row>
     <row r="114">
@@ -7397,11 +7397,11 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>7001548.26</v>
+        <v>7694.91</v>
       </c>
     </row>
     <row r="115">
@@ -7458,11 +7458,11 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>148476.3</v>
+        <v>163.18</v>
       </c>
     </row>
     <row r="116">
@@ -7519,11 +7519,11 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>7626839.71</v>
+        <v>8382.129999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7580,11 +7580,11 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>9305800</v>
+        <v>10227.35</v>
       </c>
     </row>
     <row r="118">
@@ -7641,11 +7641,11 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>9599872.800000001</v>
+        <v>10550.55</v>
       </c>
     </row>
     <row r="119">
@@ -7702,11 +7702,11 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>4638620</v>
+        <v>5097.98</v>
       </c>
     </row>
     <row r="120">
@@ -7763,11 +7763,11 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>12842480</v>
+        <v>14114.27</v>
       </c>
     </row>
     <row r="121">
@@ -7824,11 +7824,11 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>636416.76</v>
+        <v>699.4400000000001</v>
       </c>
     </row>
     <row r="122">
@@ -7885,11 +7885,11 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>7626032.89</v>
+        <v>8381.24</v>
       </c>
     </row>
     <row r="123">
@@ -7946,11 +7946,11 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>618321.62</v>
+        <v>679.55</v>
       </c>
     </row>
     <row r="124">
@@ -8007,11 +8007,11 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>7615583.5</v>
+        <v>8369.76</v>
       </c>
     </row>
     <row r="125">
@@ -8068,17 +8068,17 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1003200.94</v>
+        <v>1102.55</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1078078-899-CM26</t>
+          <t>1078078-900-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8118,22 +8118,22 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2278612</v>
+        <v>74685.45</v>
       </c>
     </row>
     <row r="127">
@@ -8190,11 +8190,11 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>72033114.51000001</v>
+        <v>79166.56</v>
       </c>
     </row>
     <row r="128">
@@ -8251,11 +8251,11 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>6262424.98</v>
+        <v>6882.59</v>
       </c>
     </row>
     <row r="129">
@@ -8312,11 +8312,11 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>9069823</v>
+        <v>9968.01</v>
       </c>
     </row>
     <row r="130">
@@ -8373,11 +8373,11 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>18066580</v>
+        <v>19855.71</v>
       </c>
     </row>
     <row r="131">
@@ -8434,17 +8434,17 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>238474.81</v>
+        <v>262.09</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1078078-900-CM26</t>
+          <t>1078078-899-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8484,22 +8484,22 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>67955785.38</v>
+        <v>2504.26</v>
       </c>
     </row>
     <row r="133">
@@ -8556,17 +8556,17 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>410816.56</v>
+        <v>451.5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1078078-894-CM26</t>
+          <t>1078078-896-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -8617,17 +8617,17 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1033700.64</v>
+        <v>775.87</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1078078-896-CM26</t>
+          <t>1078078-894-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8678,11 +8678,11 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>705960.36</v>
+        <v>1136.07</v>
       </c>
     </row>
     <row r="136">
@@ -8739,11 +8739,11 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>11648278.11</v>
+        <v>12801.81</v>
       </c>
     </row>
     <row r="137">
@@ -8800,11 +8800,11 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8854.799999999999</v>
       </c>
     </row>
     <row r="138">
@@ -8861,11 +8861,11 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>628512.78</v>
+        <v>690.75</v>
       </c>
     </row>
     <row r="139">
@@ -8922,11 +8922,11 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>458479.63</v>
+        <v>503.88</v>
       </c>
     </row>
     <row r="140">
@@ -8983,11 +8983,11 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>8197059.15</v>
+        <v>9008.809999999999</v>
       </c>
     </row>
     <row r="141">
@@ -9044,11 +9044,11 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>518721</v>
+        <v>570.09</v>
       </c>
     </row>
     <row r="142">
@@ -9105,11 +9105,11 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>8179346</v>
+        <v>8989.35</v>
       </c>
     </row>
     <row r="143">
@@ -9166,11 +9166,11 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>126445.83</v>
+        <v>138.97</v>
       </c>
     </row>
     <row r="144">
@@ -9227,11 +9227,11 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>48435103.92</v>
+        <v>53231.64</v>
       </c>
     </row>
     <row r="145">
@@ -9288,11 +9288,11 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>558771.64</v>
+        <v>614.11</v>
       </c>
     </row>
     <row r="146">
@@ -9349,17 +9349,17 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>8003679.39</v>
+        <v>8796.280000000001</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2708-157-CM26</t>
+          <t>1078078-909-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9379,48 +9379,48 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Cancelada por Comprador</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>INVERSIONES SANTA FRANCISCA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>77.721.515-9</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1490046.6</v>
+        <v>879.86</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1078078-909-CM26</t>
+          <t>1078078-908-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9471,17 +9471,17 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>800577.26</v>
+        <v>1199.2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1078078-908-CM26</t>
+          <t>1078078-907-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9521,28 +9521,28 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1091141.94</v>
+        <v>17743.88</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1078078-907-CM26</t>
+          <t>1078078-906-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9582,28 +9582,28 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>16145034.64</v>
+        <v>41491.92</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1078078-906-CM26</t>
+          <t>758-174-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>60.509.001-k</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9643,28 +9643,28 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>37753214.1</v>
+        <v>4993.09</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>758-174-CM26</t>
+          <t>758-173-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9704,28 +9704,28 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>4543182</v>
+        <v>1409.04</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>758-173-CM26</t>
+          <t>758-172-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9765,28 +9765,28 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1282076.25</v>
+        <v>1704.31</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>758-172-CM26</t>
+          <t>758-171-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9826,28 +9826,28 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1550736.6</v>
+        <v>2916.32</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>758-171-CM26</t>
+          <t>2735-219-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>60.509.001-k</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9887,28 +9887,28 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2653539.35</v>
+        <v>1892.05</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2735-219-CM26</t>
+          <t>778992-27-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9933,43 +9933,43 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1721561.1</v>
+        <v>808.46</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>778992-27-CM26</t>
+          <t>778992-26-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10020,17 +10020,17 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>735610.4</v>
+        <v>3497.76</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>778992-26-CM26</t>
+          <t>1078078-925-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10055,43 +10055,43 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3182583.6</v>
+        <v>6970.29</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1078078-925-CM26</t>
+          <t>1078078-924-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -10131,28 +10131,28 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>6342220.43</v>
+        <v>166.01</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1078078-924-CM26</t>
+          <t>3811-69-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.071.900-2</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE ISLA DE MAIPO</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10192,28 +10192,28 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SUPERMERCADO MAYORISTA METROPOLITANO</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.047.926-6</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>151052.65</v>
+        <v>10541.24</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3811-69-CM26</t>
+          <t>1078078-923-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10233,17 +10233,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.071.900-2</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ISLA DE MAIPO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10253,28 +10253,28 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>SUPERMERCADO MAYORISTA METROPOLITANO</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>77.047.926-6</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>9591400</v>
+        <v>2739.17</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1078078-923-CM26</t>
+          <t>1078078-922-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10314,28 +10314,28 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2492350.28</v>
+        <v>8854.799999999999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1078078-922-CM26</t>
+          <t>1078078-921-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10375,28 +10375,28 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>8056924.75</v>
+        <v>2575.28</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1078078-921-CM26</t>
+          <t>2436-295-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10416,48 +10416,48 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2343226.62</v>
+        <v>976.4400000000001</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2436-295-CM26</t>
+          <t>1078078-919-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10482,43 +10482,43 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>888454</v>
+        <v>628.0700000000001</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1078078-919-CM26</t>
+          <t>1078078-918-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10558,28 +10558,28 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>571479.65</v>
+        <v>8298.379999999999</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1078078-918-CM26</t>
+          <t>2412-145-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10599,17 +10599,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10619,28 +10619,28 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.721.492-6</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>7550642.82</v>
+        <v>21417.48</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2412-145-CM26</t>
+          <t>1426095-47-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10660,48 +10660,48 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>COMERCIAL ORIONIS SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>77.721.492-6</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>19487618.5</v>
+        <v>1092.12</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1426095-47-CM26</t>
+          <t>1250355-10-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10721,48 +10721,48 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.933.800-6</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.950.108-8</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>993709.5</v>
+        <v>20316.05</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1250355-10-CM26</t>
+          <t>1078078-920-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.933.800-6</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10802,28 +10802,28 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>76.950.108-8</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>18485438.58</v>
+        <v>27028.7</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1078078-920-CM26</t>
+          <t>1078078-934-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10874,17 +10874,17 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>24593226.63</v>
+        <v>1122.66</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1078078-934-CM26</t>
+          <t>1078078-933-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10924,28 +10924,28 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1021503.14</v>
+        <v>17743.88</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1078078-933-CM26</t>
+          <t>1078078-931-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10985,28 +10985,28 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>16145034.64</v>
+        <v>538.8200000000001</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1078078-931-CM26</t>
+          <t>1078078-929-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11046,28 +11046,28 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>490270.48</v>
+        <v>41491.92</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1078078-929-CM26</t>
+          <t>1078078-930-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11107,28 +11107,28 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>37753214.1</v>
+        <v>9009.57</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1078078-930-CM26</t>
+          <t>1078078-927-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11168,28 +11168,28 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>8197742.21</v>
+        <v>462.03</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1078078-927-CM26</t>
+          <t>1078078-926-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -11229,28 +11229,28 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>420399.63</v>
+        <v>8872.120000000001</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1078078-926-CM26</t>
+          <t>2401-264-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11275,43 +11275,43 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>8072680.35</v>
+        <v>8506.23</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2401-264-CM26</t>
+          <t>3376-19-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11331,48 +11331,48 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>61.101.078-8</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIALIZADORA SANTA ELIANA SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>77.544.929-2</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>7739760</v>
+        <v>8744.52</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>3376-19-CM26</t>
+          <t>1078078-928-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.101.078-8</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11412,28 +11412,28 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIALIZADORA SANTA ELIANA SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>77.544.929-2</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>7956578</v>
+        <v>35185.14</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1078078-928-CM26</t>
+          <t>3825-80-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.261.400-3</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11473,28 +11473,28 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>32014717.56</v>
+        <v>2668.01</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3825-80-CM26</t>
+          <t>2403-127-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11519,12 +11519,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.261.400-3</t>
+          <t>69.254.000-k</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
+          <t>I MUNICIPALIDAD DE PENALOLEN</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11534,28 +11534,28 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>COMERCIALIZADORA GASSET DEL VALLE SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>77.292.846-7</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2427600</v>
+        <v>54831.17</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2403-127-CM26</t>
+          <t>1078078-944-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>69.254.000-k</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENALOLEN</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11595,28 +11595,28 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA GASSET DEL VALLE SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>77.292.846-7</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>49890512</v>
+        <v>2476.38</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1078078-944-CM26</t>
+          <t>2297-336-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11636,48 +11636,48 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2253242.39</v>
+        <v>3233.13</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2297-336-CM26</t>
+          <t>1078078-949-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11697,48 +11697,48 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2941799</v>
+        <v>1460.21</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1078078-949-CM26</t>
+          <t>1078078-948-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11778,28 +11778,28 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1328635</v>
+        <v>865.35</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1078078-948-CM26</t>
+          <t>1078078-947-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11850,17 +11850,17 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>787374.21</v>
+        <v>1376.99</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1078078-947-CM26</t>
+          <t>1078078-946-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11900,28 +11900,28 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1252915.3</v>
+        <v>8801.23</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1078078-946-CM26</t>
+          <t>1078078-945-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11961,28 +11961,28 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>8008179.97</v>
+        <v>903</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1078078-945-CM26</t>
+          <t>1078078-943-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12022,28 +12022,28 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>821633.12</v>
+        <v>657.63</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1078078-943-CM26</t>
+          <t>1078078-950-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12083,28 +12083,28 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>598371.27</v>
+        <v>5024.91</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1078078-950-CM26</t>
+          <t>1078078-941-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12144,28 +12144,28 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>4572129.94</v>
+        <v>1453.89</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1078078-941-CM26</t>
+          <t>5349-540-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12190,43 +12190,43 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1322888.49</v>
+        <v>1291.55</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5349-540-CM26</t>
+          <t>1078078-935-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12251,43 +12251,43 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1175172.6</v>
+        <v>8854.799999999999</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1078078-935-CM26</t>
+          <t>1078078-936-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12327,28 +12327,28 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>8056924.75</v>
+        <v>728.15</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1078078-936-CM26</t>
+          <t>1078078-942-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12388,28 +12388,28 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>662538.45</v>
+        <v>8854.799999999999</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1078078-942-CM26</t>
+          <t>1078078-938-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12429,7 +12429,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -12449,28 +12449,28 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>8056924.75</v>
+        <v>8298.379999999999</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1078078-938-CM26</t>
+          <t>1078078-939-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12490,7 +12490,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -12521,17 +12521,17 @@
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>7550642.82</v>
+        <v>495.53</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1078078-939-CM26</t>
+          <t>1078078-940-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12551,7 +12551,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -12582,17 +12582,17 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>450880.29</v>
+        <v>8381.24</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1078078-940-CM26</t>
+          <t>1078078-937-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -12632,28 +12632,28 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>7626032.89</v>
+        <v>7900.7</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1078078-937-CM26</t>
+          <t>1078078-959-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12693,28 +12693,28 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>7188795.95</v>
+        <v>17600.6</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1078078-962-CM26</t>
+          <t>1078078-958-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -12754,28 +12754,28 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>8673704.130000001</v>
+        <v>547.54</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1078078-958-CM26</t>
+          <t>1078078-957-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12815,28 +12815,28 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>498205.4</v>
+        <v>8800.299999999999</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2793-226-CM26</t>
+          <t>1078078-956-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12856,17 +12856,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Solicitud de Cancelacion</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12876,28 +12876,28 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>ANA ISABEL MARIAN BAHAMONDES</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>10.991.344-8</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2997978.9</v>
+        <v>8298.379999999999</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1078078-957-CM26</t>
+          <t>1078078-962-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12917,7 +12917,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -12937,28 +12937,28 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>8007333.88</v>
+        <v>9532.66</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1078078-956-CM26</t>
+          <t>1078078-954-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13009,17 +13009,17 @@
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>7550642.82</v>
+        <v>776.78</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1078078-959-CM26</t>
+          <t>1078078-953-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13070,17 +13070,17 @@
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>16014667.76</v>
+        <v>8800.299999999999</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1078078-954-CM26</t>
+          <t>1078078-952-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13131,17 +13131,17 @@
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>706783.84</v>
+        <v>290.11</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1078078-953-CM26</t>
+          <t>1078078-951-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13181,28 +13181,28 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>8007333.88</v>
+        <v>198.63</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1078078-952-CM26</t>
+          <t>1078078-955-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13253,17 +13253,17 @@
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>263970.56</v>
+        <v>8298.379999999999</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1078078-955-CM26</t>
+          <t>1078078-965-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -13314,17 +13314,17 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>7550642.82</v>
+        <v>2500.31</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1078078-951-CM26</t>
+          <t>1078078-964-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -13375,17 +13375,17 @@
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>180731.25</v>
+        <v>2058.52</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1078078-965-CM26</t>
+          <t>1078078-963-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13425,28 +13425,28 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2275018.2</v>
+        <v>19346.22</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1078078-964-CM26</t>
+          <t>2387-125-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13466,48 +13466,48 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1873029.06</v>
+        <v>1444.83</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1078078-963-CM26</t>
+          <t>2483-117-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13527,17 +13527,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13547,28 +13547,28 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>17602991.7</v>
+        <v>7690</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2387-125-CM26</t>
+          <t>1078078-961-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13588,48 +13588,48 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1314640.6</v>
+        <v>651.61</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2483-117-CM26</t>
+          <t>1078078-960-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13649,17 +13649,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13669,28 +13669,28 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>6997075.05</v>
+        <v>2005.54</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1078078-961-CM26</t>
+          <t>1078078-974-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -13730,28 +13730,28 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>592893.7</v>
+        <v>3520.62</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1078078-960-CM26</t>
+          <t>2674-257-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13791,28 +13791,28 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1824831.68</v>
+        <v>36112.59</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1078078-974-CM26</t>
+          <t>1078078-968-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13852,28 +13852,28 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>3203384.8</v>
+        <v>223.9</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2674-257-CM26</t>
+          <t>1078078-969-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13893,17 +13893,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13913,28 +13913,28 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>32858601.3</v>
+        <v>17709.61</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1078078-968-CM26</t>
+          <t>1078078-970-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13985,17 +13985,17 @@
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>203728</v>
+        <v>1628.86</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1078078-969-CM26</t>
+          <t>1079505-105-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14015,48 +14015,48 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>16113849.5</v>
+        <v>4115.14</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1078078-970-CM26</t>
+          <t>4562-157-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14076,48 +14076,48 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1482091.45</v>
+        <v>10863.88</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1079505-105-CM26</t>
+          <t>1078078-971-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14142,43 +14142,43 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>3744335</v>
+        <v>451.8</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>4562-157-CM26</t>
+          <t>1078078-972-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14203,43 +14203,43 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>9884973</v>
+        <v>18017.63</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1078078-971-CM26</t>
+          <t>1078078-973-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14279,28 +14279,28 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>411093.83</v>
+        <v>1145.62</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1078078-972-CM26</t>
+          <t>1426095-55-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -14325,43 +14325,43 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>16394118.3</v>
+        <v>772.15</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1078078-973-CM26</t>
+          <t>758-219-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -14386,12 +14386,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>60.509.001-k</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14401,28 +14401,28 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1042391.21</v>
+        <v>6802.12</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1426095-55-CM26</t>
+          <t>1285502-5-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14442,22 +14442,22 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14473,17 +14473,17 @@
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>702576</v>
+        <v>330.23</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1285502-5-CM26</t>
+          <t>1078078-976-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -14508,43 +14508,43 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>300475</v>
+        <v>264.68</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>758-219-CM26</t>
+          <t>1078078-977-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14559,22 +14559,22 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>60.509.001-k</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14595,17 +14595,17 @@
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>6189201.9</v>
+        <v>657.27</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1078078-976-CM26</t>
+          <t>1078078-978-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14645,28 +14645,28 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>240827.44</v>
+        <v>8800.299999999999</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1078078-977-CM26</t>
+          <t>1078078-979-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -14706,28 +14706,28 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>598049.97</v>
+        <v>1310.93</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1078078-978-CM26</t>
+          <t>1078078-980-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14767,28 +14767,28 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>8007333.88</v>
+        <v>353.17</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1078078-979-CM26</t>
+          <t>837-172-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14828,28 +14828,28 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1192806.02</v>
+        <v>21841.02</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1078078-980-CM26</t>
+          <t>2341-126-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14864,22 +14864,22 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14889,28 +14889,28 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>321342.84</v>
+        <v>18102.76</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>837-172-CM26</t>
+          <t>1078078-987-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -14935,12 +14935,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.003.000-9</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>SERVICIO MEDICO LEGAL</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -14950,28 +14950,28 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>19873000</v>
+        <v>1937.29</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2341-126-CM26</t>
+          <t>1078078-986-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14991,17 +14991,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15011,28 +15011,28 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>16471578.97</v>
+        <v>538.8200000000001</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1078078-987-CM26</t>
+          <t>4201-134-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15057,12 +15057,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.073.900-3</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE CURACAVI</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15072,28 +15072,28 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1762723.2</v>
+        <v>9220.309999999999</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1078078-986-CM26</t>
+          <t>1078078-984-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15133,28 +15133,28 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>490270.48</v>
+        <v>6583.51</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>4201-134-CM26</t>
+          <t>1078078-983-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15179,12 +15179,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>69.073.900-3</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAVI</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15194,28 +15194,28 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>8389500</v>
+        <v>254.74</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1078078-984-CM26</t>
+          <t>1078078-982-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15255,28 +15255,28 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>5990294.59</v>
+        <v>1059.5</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1078078-983-CM26</t>
+          <t>1078078-981-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15316,28 +15316,28 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>ABATTE OFFICITY</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>96.909.950-0</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>231782.25</v>
+        <v>8641.139999999999</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1078078-982-CM26</t>
+          <t>1078078-985-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15357,7 +15357,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -15377,28 +15377,28 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>964028.52</v>
+        <v>9009.57</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1078078-981-CM26</t>
+          <t>1078078-996-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -15438,28 +15438,28 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>ABATTE OFFICITY</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>96.909.950-0</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>7862513.26</v>
+        <v>9304.120000000001</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1078078-985-CM26</t>
+          <t>2341-134-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -15484,12 +15484,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15499,28 +15499,28 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>8197742.21</v>
+        <v>32527.43</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1078078-996-CM26</t>
+          <t>1078078-999-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15560,28 +15560,28 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>8465759.960000001</v>
+        <v>560.64</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2341-134-CM26</t>
+          <t>1078078-998-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15606,12 +15606,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15621,28 +15621,28 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>29596490</v>
+        <v>658.4299999999999</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1078078-999-CM26</t>
+          <t>1078078-997-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15682,28 +15682,28 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>510125.63</v>
+        <v>493.4</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1078078-998-CM26</t>
+          <t>1078078-995-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -15743,28 +15743,28 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>599103.12</v>
+        <v>493.4</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1078078-997-CM26</t>
+          <t>1078078-990-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15815,17 +15815,17 @@
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>448944.16</v>
+        <v>2648.99</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1078078-995-CM26</t>
+          <t>1078078-993-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15865,28 +15865,28 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>448944.16</v>
+        <v>2496.61</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1078078-990-CM26</t>
+          <t>1078078-992-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -15926,28 +15926,28 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>Forestal y Comercial Arbolito Ltda.</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.038.610-1</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2410302.16</v>
+        <v>18434.61</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1078078-993-CM26</t>
+          <t>1078078-991-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15998,17 +15998,17 @@
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2271649.31</v>
+        <v>2315.51</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1078078-992-CM26</t>
+          <t>1078078-989-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16048,28 +16048,28 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Forestal y Comercial Arbolito Ltda.</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>77.038.610-1</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>16773526</v>
+        <v>461.94</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1078078-991-CM26</t>
+          <t>1078078-988-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16109,28 +16109,28 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2106866.44</v>
+        <v>8800.299999999999</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1078078-989-CM26</t>
+          <t>1078078-994-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16170,28 +16170,28 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>420312.76</v>
+        <v>9304.120000000001</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1078078-988-CM26</t>
+          <t>1078078-1002-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -16231,28 +16231,28 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>MIVIVIENDA SPA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.897.437-3</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>8007333.88</v>
+        <v>8854.799999999999</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1078078-994-CM26</t>
+          <t>1078078-1003-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16267,7 +16267,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -16292,28 +16292,28 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>8465759.960000001</v>
+        <v>1096.24</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1078078-1002-CM26</t>
+          <t>1078078-1001-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -16353,28 +16353,28 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>MIVIVIENDA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>76.897.437-3</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>8056924.75</v>
+        <v>728.16</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1078078-1003-CM26</t>
+          <t>2385-198-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16394,48 +16394,48 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>997460.38</v>
+        <v>1075.61</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1078078-1001-CM26</t>
+          <t>2080-2942-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16455,48 +16455,48 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>60.509.001-K</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>662544.4</v>
+        <v>1174.38</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2385-198-CM26</t>
+          <t>1063796-7-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16521,43 +16521,43 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.150.400-k</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>978685.75</v>
+        <v>15477.64</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2080-2942-CM26</t>
+          <t>1078078-1000-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16577,48 +16577,48 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>60.509.001-K</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1068558.12</v>
+        <v>1926.9</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1063796-7-CM26</t>
+          <t>2385-200-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16643,159 +16643,37 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>69.150.400-k</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>14082995.5</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>1078078-1000-CM26</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>mar-2026</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>60.509.001-K</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M267" s="2" t="n">
-        <v>1753274.6</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>2385-200-CM26</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>mar-2026</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>69.020.200-K</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>77.325.352-8</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M268" s="2" t="n">
-        <v>1357492.5</v>
+        <v>1491.93</v>
       </c>
     </row>
   </sheetData>
